--- a/Result/profitability/2905.xlsx
+++ b/Result/profitability/2905.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003750000000000003</v>
+        <v>0.3625</v>
       </c>
       <c r="N2" t="n">
-        <v>9.241250000000001</v>
+        <v>11.3175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.39625</v>
       </c>
       <c r="N3" t="n">
-        <v>8.0075</v>
+        <v>18.3875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.21375</v>
+        <v>0.45625</v>
       </c>
       <c r="N4" t="n">
-        <v>15.3625</v>
+        <v>21.3925</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13875</v>
+        <v>2.10125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.8625</v>
+        <v>13.59125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.17</v>
+        <v>0.33375</v>
       </c>
       <c r="N6" t="n">
-        <v>6.963749999999999</v>
+        <v>7.90375</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1325</v>
+        <v>0.34625</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6925</v>
+        <v>10.67375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24875</v>
+        <v>0.4825</v>
       </c>
       <c r="N8" t="n">
-        <v>9.82</v>
+        <v>14.49375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9332,42 +9332,42 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>65821</v>
+        <v>36872</v>
       </c>
       <c r="D71" t="n">
-        <v>2679</v>
+        <v>9044</v>
       </c>
       <c r="E71" t="n">
-        <v>63142</v>
+        <v>27828</v>
       </c>
       <c r="F71" t="n">
-        <v>95.93000000000001</v>
+        <v>75.47</v>
       </c>
       <c r="G71" t="n">
-        <v>58724</v>
+        <v>24943</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>89.22%</t>
+          <t>67.65%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-59979</v>
+        <v>-73918</v>
       </c>
       <c r="J71" t="n">
-        <v>-1255</v>
+        <v>-48975</v>
       </c>
       <c r="K71" t="n">
-        <v>-57</v>
+        <v>-14626</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.05</v>
+        <v>-13.77</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.04749999999999998</v>
+        <v>-1.7625</v>
       </c>
       <c r="N71" t="n">
-        <v>6.461250000000001</v>
+        <v>3.90375</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9394,28 +9394,28 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.04</v>
+        <v>-13.76</v>
       </c>
       <c r="X71" t="n">
-        <v>4</v>
+        <v>1376</v>
       </c>
       <c r="Y71" t="n">
-        <v>102.87</v>
+        <v>82.41</v>
       </c>
       <c r="Z71" t="n">
-        <v>-14.82276657060519</v>
+        <v>-11.87463976945245</v>
       </c>
       <c r="AA71" t="n">
-        <v>-1.29</v>
+        <v>-15.01</v>
       </c>
       <c r="AB71" t="n">
-        <v>-1.040322580645161</v>
+        <v>-12.10483870967742</v>
       </c>
       <c r="AC71" t="n">
-        <v>105.11</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="AD71" t="n">
-        <v>-11.44989106753813</v>
+        <v>-9.221132897603486</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9459,42 +9459,42 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>48814</v>
+        <v>77763</v>
       </c>
       <c r="D72" t="n">
-        <v>41945</v>
+        <v>35580</v>
       </c>
       <c r="E72" t="n">
-        <v>6869</v>
+        <v>42182</v>
       </c>
       <c r="F72" t="n">
-        <v>14.07</v>
+        <v>54.24</v>
       </c>
       <c r="G72" t="n">
-        <v>3112</v>
+        <v>36893</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>47.44%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>-1803</v>
+        <v>12136</v>
       </c>
       <c r="J72" t="n">
-        <v>1309</v>
+        <v>49029</v>
       </c>
       <c r="K72" t="n">
-        <v>622</v>
+        <v>15192</v>
       </c>
       <c r="L72" t="n">
-        <v>0.59</v>
+        <v>14.34</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.13125</v>
+        <v>-0.1274999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>14.24625</v>
+        <v>16.71</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -9521,28 +9521,28 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.64</v>
+        <v>28.11</v>
       </c>
       <c r="X72" t="n">
-        <v>-12.8</v>
+        <v>-2.041394335511983</v>
       </c>
       <c r="Y72" t="n">
-        <v>-81.86000000000001</v>
+        <v>-21.23</v>
       </c>
       <c r="Z72" t="n">
-        <v>-0.8533305535286146</v>
+        <v>-0.28130382933616</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.53</v>
+        <v>15.28</v>
       </c>
       <c r="AB72" t="n">
-        <v>-1.627659574468085</v>
+        <v>-16.25531914893617</v>
       </c>
       <c r="AC72" t="n">
-        <v>-10.62</v>
+        <v>29.55</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.4301336573511544</v>
+        <v>1.196840826245444</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9554,14 +9554,14 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9618,10 +9618,10 @@
         <v>0.19</v>
       </c>
       <c r="M73" t="n">
-        <v>0.2675</v>
+        <v>0.27125</v>
       </c>
       <c r="N73" t="n">
-        <v>5.021250000000001</v>
+        <v>7.485000000000001</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9648,16 +9648,16 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.4</v>
+        <v>-14.15</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.6779661016949152</v>
+        <v>-0.9867503486750349</v>
       </c>
       <c r="Y73" t="n">
-        <v>-24.33</v>
+        <v>-64.5</v>
       </c>
       <c r="Z73" t="n">
-        <v>-1.729211087420043</v>
+        <v>-1.189159292035398</v>
       </c>
       <c r="AA73" t="n">
         <v>0.34</v>
@@ -9745,10 +9745,10 @@
         <v>0.03</v>
       </c>
       <c r="M74" t="n">
-        <v>0.1125</v>
+        <v>0.11625</v>
       </c>
       <c r="N74" t="n">
-        <v>6.34625</v>
+        <v>8.81</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>65504</v>
+      </c>
+      <c r="D75" t="n">
+        <v>51362</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10658</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4493</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6164</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2006</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.65625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X75" t="n">
+        <v>62.33333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.366455696202531</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.137981118373275</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-53.88</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7139260633364251</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
